--- a/registration_forms/040_school_trip_authorization_form--registration_forms.xlsx
+++ b/registration_forms/040_school_trip_authorization_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>grade_1</t>
+          <t>grade 1</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>grade_2</t>
+          <t>grade 2</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>grade_3</t>
+          <t>grade 3</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>grade_4</t>
+          <t>grade 4</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>grade_5</t>
+          <t>grade 5</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>grade_6</t>
+          <t>grade 6</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>grade_7</t>
+          <t>grade 7</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>grade_8</t>
+          <t>grade 8</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>grade_9</t>
+          <t>grade 9</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>grade_10</t>
+          <t>grade 10</t>
         </is>
       </c>
     </row>
